--- a/data/Research Papers.xlsx
+++ b/data/Research Papers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/strahinja/Desktop/TFM/Research papers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljaljevi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559085EF-30C4-E34B-879B-9C1E185D9AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74241B7C-A71A-4B60-B204-E806CCE1BCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="34200" windowHeight="19780" xr2:uid="{027DABDA-E301-6248-9EF5-B2B8807799A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{027DABDA-E301-6248-9EF5-B2B8807799A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw Main Research'!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="269">
   <si>
     <t>Title</t>
   </si>
@@ -1206,40 +1206,136 @@
     <t>2025</t>
   </si>
   <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
+    <t>Leveraging Large Language Models for Code Translation and Software Development in Scientific Computing</t>
+  </si>
+  <si>
+    <t>DhruvDubey2025CodeTranslation</t>
+  </si>
+  <si>
+    <t>Dhruv, Akash and Dubey, Anshu</t>
+  </si>
+  <si>
+    <t>Code Generation, Challenges &amp; Landscape</t>
+  </si>
+  <si>
+    <t>Fortran2CPP: Automating Fortran-to-C++ Translation using LLMs via Multi-Turn Dialogue and Dual-Agent Integration</t>
+  </si>
+  <si>
+    <t>Chen2024Fortran2CPP</t>
+  </si>
+  <si>
+    <t>Le Chen and Bin Lei and Dunzhi Zhou and Pei{-}Hung Lin and Chunhua Liao and Caiwen Ding and Ali Jannesari</t>
+  </si>
+  <si>
+    <t>ChatHPC: Building the Foundations for a Productive and Trustworthy AI-Assisted HPC Ecosystem</t>
+  </si>
+  <si>
+    <t>ValeroLara2025ChatHPC</t>
+  </si>
+  <si>
+    <t>Pedro Valero Lara and Aaron Young and Jeffrey S. Vetter and Zheming Jin and Swaroop Pophale and Mohammad Alaul Haque Monil and Keita Teranishi and William F. Godoy</t>
+  </si>
+  <si>
+    <t>ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads</t>
+  </si>
+  <si>
+    <t>ValeroLara2026ChatMPI</t>
+  </si>
+  <si>
+    <t>Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy</t>
+  </si>
+  <si>
+    <t>Parallelization &amp; Optimization, Code Generation, Frameworks &amp; Architectures</t>
+  </si>
+  <si>
+    <t>{PRAGMA}: A Profiling-Reasoned Multi-Agent Framework for Automatic Kernel Optimization</t>
+  </si>
+  <si>
+    <t>Lei2025PRAGMA</t>
+  </si>
+  <si>
+    <t>Kelun Lei and Hailong Yang and Huaitao Zhang and Xin You and Kaige Zhang and Zhongzhi Luan and Yi Liu and Depei Qian</t>
+  </si>
+  <si>
+    <t>Parallelization &amp; Optimization, Frameworks &amp; Architectures</t>
+  </si>
+  <si>
+    <t>Leveraging LLMs to Automate Energy-Aware Refactoring of Parallel Scientific Codes</t>
+  </si>
+  <si>
+    <t>Dearing2025LASSIEE</t>
+  </si>
+  <si>
+    <t>Matthew T. Dearing and Yiheng Tao and Xingfu Wu and Zhiling Lan and Valerie Taylor</t>
+  </si>
+  <si>
+    <t>LLM-HPC++: Evaluating LLM-Generated Modern C++ and MPI+OpenMP Codes for Scalable Mandelbrot Set Computation</t>
+  </si>
+  <si>
+    <t>Diehl2025LLMHPCpp</t>
+  </si>
+  <si>
+    <t>Patrick Diehl and Noujoud Nader and Deepti Gupta</t>
+  </si>
+  <si>
+    <t>Adding New Capability in Existing Scientific Application with LLM Assistance</t>
+  </si>
+  <si>
+    <t>DubeyDhruv2025NewCapability</t>
+  </si>
+  <si>
+    <t>Anshu Dubey and Akash Dhruv</t>
+  </si>
+  <si>
+    <t>{PEAK}: A Performance Engineering AI-Assistant for GPU Kernels Powered by Natural Language Transformations</t>
+  </si>
+  <si>
+    <t>Tariq2025PEAK</t>
+  </si>
+  <si>
+    <t>Muhammad Usman Tariq and Abhinav Jangda and Angelica Moreira and Madan Musuvathi and Tyler Sorensen</t>
+  </si>
+  <si>
+    <t>Chat{PORT}: Fine-Tuned {LLM} for Easy Code {PORT}ing</t>
+  </si>
+  <si>
+    <t>Pophale2026ChatPORT</t>
+  </si>
+  <si>
+    <t>Swaroop Pophale and Zheming Jin and Keita Teranishi</t>
+  </si>
+  <si>
+    <t>Code Generation, Frameworks &amp; Architectures</t>
+  </si>
+  <si>
+    <t>Enhancing Chat{PORT} with {CUDA}-to-{SYCL} Kernel Translation Capability</t>
+  </si>
+  <si>
+    <t>Jin2025ChatPORTCudaSyCL</t>
+  </si>
+  <si>
+    <t>Zheming Jin and Swaroop Pophale and Keita Teranishi</t>
+  </si>
+  <si>
+    <t>{PCEBench}: A Multi-Dimensional Benchmark for Evaluating Large Language Models in Parallel Code Generation</t>
+  </si>
+  <si>
+    <t>Chen2025PCEBench</t>
+  </si>
+  <si>
+    <t>L. Chen and N. Ahmed and M. Capot{\u{a}} and T. Willke and N. Hasabnis and A. Jannesari</t>
+  </si>
+  <si>
+    <t>{UniPar}: A Unified LLM-Based Framework for Parallel and Accelerated Code Translation in {HPC}</t>
+  </si>
+  <si>
+    <t>Bitan2025UniPar</t>
+  </si>
+  <si>
+    <t>Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1404,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1342,15 +1438,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="7"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color theme="7"/>
       </bottom>
@@ -1369,7 +1456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1395,23 +1482,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1547,6 +1628,63 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0"/>
+              <c:y val="6.685510405806129E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1578,7 +1716,39 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-EA81-4FD4-8DBD-4FC885948BA9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="6.685510405806129E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-EA81-4FD4-8DBD-4FC885948BA9}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1634,136 +1804,42 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'Timeline Main Research'!$D$9:$D$34</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="22"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Oct</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Dec</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Mar</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Apr</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Jul</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Aug</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Oct</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>Dec</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Mar</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Apr</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2023</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>2024</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>2025</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>'Timeline Main Research'!$D$9:$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Timeline Main Research'!$E$9:$E$34</c:f>
+              <c:f>'Timeline Main Research'!$E$9:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1970,8 +2046,6 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -2532,15 +2606,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2425700</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:colOff>1943847</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>95997</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>813547</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2569,22 +2643,22 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Strahinja Ljaljevic" refreshedDate="45880.45682615741" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{7E58EB42-7530-3042-8255-3A940C0AEDDC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ljaljevic, Strahinja" refreshedDate="46141.403660532407" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{7E58EB42-7530-3042-8255-3A940C0AEDDC}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G29" sheet="Raw Main Research"/>
   </cacheSource>
-  <cacheFields count="10">
+  <cacheFields count="9">
     <cacheField name="Title" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Key" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Author(s)" numFmtId="0">
-      <sharedItems containsBlank="1" longText="1"/>
+      <sharedItems longText="1"/>
     </cacheField>
     <cacheField name="Year" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2025-06-29T00:00:00" count="24">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2026-01-26T00:00:00" count="33">
         <d v="2024-02-01T00:00:00"/>
         <d v="2024-05-01T00:00:00"/>
         <d v="2023-10-01T00:00:00"/>
@@ -2600,35 +2674,41 @@
         <d v="2025-06-26T00:00:00"/>
         <d v="2025-04-21T00:00:00"/>
         <d v="2025-03-15T00:00:00"/>
-        <d v="2023-11-01T00:00:00"/>
-        <d v="2023-12-01T00:00:00"/>
-        <d v="2024-01-01T00:00:00"/>
-        <d v="2024-03-01T00:00:00"/>
-        <d v="2024-04-01T00:00:00"/>
-        <d v="2024-06-01T00:00:00"/>
-        <d v="2024-07-01T00:00:00"/>
-        <d v="2024-09-01T00:00:00"/>
-        <d v="2024-10-01T00:00:00"/>
+        <d v="2025-06-01T00:00:00"/>
+        <d v="2024-12-27T00:00:00"/>
+        <d v="2025-11-15T00:00:00"/>
+        <d v="2026-01-25T00:00:00"/>
+        <d v="2025-11-09T00:00:00"/>
+        <d v="2025-05-04T00:00:00"/>
+        <d v="2025-12-18T00:00:00"/>
+        <d v="2025-10-30T00:00:00"/>
+        <d v="2025-12-22T00:00:00"/>
+        <d v="2023-11-01T00:00:00" u="1"/>
+        <d v="2023-12-01T00:00:00" u="1"/>
+        <d v="2024-01-01T00:00:00" u="1"/>
+        <d v="2024-03-01T00:00:00" u="1"/>
+        <d v="2024-04-01T00:00:00" u="1"/>
+        <d v="2024-06-01T00:00:00" u="1"/>
+        <d v="2024-07-01T00:00:00" u="1"/>
+        <d v="2024-09-01T00:00:00" u="1"/>
+        <d v="2024-10-01T00:00:00" u="1"/>
       </sharedItems>
-      <fieldGroup par="9"/>
+      <fieldGroup par="8"/>
     </cacheField>
     <cacheField name="PaperType" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Included?" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Key Insights" numFmtId="0">
-      <sharedItems containsBlank="1" longText="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Months (Year)" numFmtId="0" databaseField="0">
       <fieldGroup base="3">
-        <rangePr groupBy="months" startDate="2023-09-01T00:00:00" endDate="2025-06-29T00:00:00"/>
+        <rangePr groupBy="months" startDate="2023-09-01T00:00:00" endDate="2026-01-26T00:00:00"/>
         <groupItems count="14">
-          <s v="&lt;9/1/23"/>
+          <s v="&lt;9/1/2023"/>
           <s v="Jan"/>
           <s v="Feb"/>
           <s v="Mar"/>
@@ -2641,19 +2721,20 @@
           <s v="Oct"/>
           <s v="Nov"/>
           <s v="Dec"/>
-          <s v="&gt;6/29/25"/>
+          <s v="&gt;1/26/2026"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
     <cacheField name="Years (Year)" numFmtId="0" databaseField="0">
       <fieldGroup base="3">
-        <rangePr groupBy="years" startDate="2023-09-01T00:00:00" endDate="2025-06-29T00:00:00"/>
-        <groupItems count="5">
-          <s v="&lt;9/1/23"/>
+        <rangePr groupBy="years" startDate="2023-09-01T00:00:00" endDate="2026-01-26T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;9/1/2023"/>
           <s v="2023"/>
           <s v="2024"/>
           <s v="2025"/>
-          <s v="&gt;6/29/25"/>
+          <s v="2026"/>
+          <s v="&gt;1/26/2026"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
@@ -2676,7 +2757,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Challenges &amp; Landscape"/>
-    <s v="This position paper explores the growing intersection between High Performance Computing (HPC) and Large Language Models (LLMs), identifying key challenges, research gaps, and future directions. It provides a meta-level survey of existing work and structures the landscape around four emerging HPC application domains where LLMs are likely to play a central role:_x000a__x0009_1._x0009_AI for HPC: Using LLMs to assist with parallel code generation, system operations, debugging._x000a__x0009_2._x0009_HPC for AI: Leveraging HPC infrastructure to train large models._x000a__x0009_3._x0009_Co-design of HPC and LLMs: Hardware and software alignment._x000a__x0009_4._x0009_HPC research through LLMs: How LLMs can accelerate scientific discovery._x000a__x000a_Main Contributions:_x000a__x0009_•_x0009_Proposes a taxonomy of how LLMs interact with HPC across different levels:_x000a__x0009_•_x0009_Programming_x000a__x0009_•_x0009_System operations_x000a__x0009_•_x0009_Workflow orchestration_x000a__x0009_•_x0009_User support (e.g., code co-pilots, documentation assistants)_x000a__x0009_•_x0009_Provides meta-analysis of state-of-the-art research, identifying fragmented efforts in:_x000a__x0009_•_x0009_Code generation (e.g., OpenMP, MPI)_x000a__x0009_•_x0009_Performance optimization (e.g., vectorization, memory locality)_x000a__x0009_•_x0009_Framework development (e.g., ChatHPC, LLM-HPC)_x000a__x000a_Conclusions:_x000a__x0009_1._x0009_HPC+LLMs is a promising but underdeveloped space, currently fragmented and lacking standardization._x000a__x0009_2._x0009_Emphasizes the need for large-scale, open datasets and pipelines to enable reliable progress._x000a__x0009_3._x0009_Calls for community-wide efforts to define benchmarks, share evaluation practices, and co-design LLM-HPC systems._x000a__x0009_4._x0009_Suggests that the greatest impact may come from hybrid systems, where LLMs guide but don’t replace human experts."/>
   </r>
   <r>
     <s v="Can Large Language Models Write Parallel Code?"/>
@@ -2686,7 +2766,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Evaluation &amp; Benchmarking, Code Generation"/>
-    <s v="Objective:_x000a_To evaluate how well current Large Language Models (LLMs) can generate and translate parallel code, which is significantly more complex than serial code due to issues like data distribution, concurrency bugs, and scalability._x000a__x000a_Methodology:_x000a__x0009_•_x0009_Introduced ParEval, a novel benchmark suite with:_x000a__x0009_•_x0009_420 prompts across_x000a__x0009_•_x0009_12 computational problem types and_x000a__x0009_•_x0009_7 execution models: Serial, OpenMP, MPI, MPI+OpenMP, Kokkos, CUDA, HIP._x000a_Tasks involve both code generation (from scratch) and code translation (from one model to another)._x000a_Assessed using:_x000a__x0009_•_x0009_Correctness: pass@1, pass@k metrics._x000a__x0009_•_x0009_Performance: speedupₙ@k and efficiencyₙ@k._x000a__x000a__x0009_•_x0009_All LLMs perform significantly worse on parallel prompts compared to serial._x000a__x0009_•_x0009_GPT-3.5 outperforms GPT-4 on parallel code generation, despite GPT-4 being newer and generally stronger elsewhere._x000a__x000a_Breakdown by Execution Models:_x000a__x0009_•_x0009_Best-performing: OpenMP and Kokkos (due to their similarity with serial code)._x000a__x0009_•_x0009_Worst-performing: MPI and MPI+OpenMP (high complexity, different code structure)._x000a__x000a_ Breakdown by Problem Types:_x000a__x0009_•_x0009_Easiest for LLMs: Transform, Search, Reduce (simple and data-parallel)._x000a__x0009_•_x0009_Hardest: Sparse Linear Algebra, FFT, Geometry, Scan, Sort (complex structure, irregular patterns)._x000a__x000a__x0009_•_x0009_GPT-4 produces the fastest code on average, but not the most correct (that’s GPT-3.5)._x000a__x0009_•_x0009_Efficiency (use of parallel resources) is low for all models (≤13%), indicating suboptimal scaling despite correctness._x000a__x000a__x0009_•_x0009_Translation often improves correctness, especially for smaller LLMs._x000a__x0009_•_x0009_Performance does not improve proportionally — translated code is not significantly more efficient._x000a__x000a_Conclusions_x000a__x0009_1._x0009_LLMs can generate correct parallel code, but success depends on the execution model and problem type._x000a__x0009_2._x0009_Parallel code generation is much harder than serial — even GPT-4 performs below 40% pass@1._x000a__x0009_3._x0009_Performance is generally low even for correct outputs. Most models do not scale efficiently._x000a__x0009_4._x0009_Providing an example (translation tasks) helps smaller LLMs significantly._x000a__x0009_5._x0009_Phind-CodeLlama-V2 offers a promising open-source alternative, approaching closed-source performance._x000a__x0009_6._x0009_Future needs: More fine-tuning on parallel/HPC data, architectural support for planning/reasoning, and better modeling of performance."/>
   </r>
   <r>
     <s v="HPC-Coder: Modeling Parallel Programs using Large Language Models"/>
@@ -2696,7 +2775,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization, Code Generation"/>
-    <s v="Objective:_x000a_To explore how LLMs can be fine-tuned to improve their capabilities in generating parallel code, particularly for OpenMP and MPI, and to introduce HPC-Coder, a fine-tuned LLaMA2 model adapted specifically for parallel programming tasks._x000a__x000a_Methodology:_x000a__x0009_•_x0009_Introduced a new benchmark suite consisting of:_x000a__x0009_•_x0009_1,639 parallel code samples_x000a__x0009_•_x0009_Across 9 domains and 2 programming paradigms (OpenMP and MPI)_x000a_Tasks:_x000a__x0009_•_x0009_Code generation from docstrings_x000a__x0009_•_x0009_Evaluation through functional correctness_x000a__x0009_•_x0009_Compared HPC-Coder (fine-tuned LLaMA2-7B) against:_x000a__x0009_•_x0009_GPT-3.5_x000a__x0009_•_x0009_GPT-4_x000a__x0009_•_x0009_CodeLlama_x000a__x0009_•_x0009_StarCoder_x000a__x000a__x0009_•_x0009_HPC-Coder outperforms all baseline models in both OpenMP and MPI._x000a__x0009_•_x0009_The improvement is particularly notable in MPI, where correctness jumped by ~15% over GPT-4._x000a__x0009_•_x0009_Open-source LLMs (CodeLlama, StarCoder) lag significantly behind the fine-tuned HPC-Coder and closed-source GPTs._x000a__x000a__x0009_•_x0009_Scientific computation domains (e.g., Matrix, Sort, Search) are where HPC-Coder shows the largest gains._x000a__x0009_•_x0009_Reasoning-intensive or irregular problems remain a challenge even for HPC-Coder._x000a__x000a_Conclusions_x000a__x0009_1._x0009_HPC-Coder sets a new state-of-the-art for generating correct parallel code in OpenMP and MPI._x000a__x0009_2._x0009_Fine-tuning on specialized data greatly boosts performance over general-purpose models like GPT-4._x000a__x0009_3._x0009_Demonstrates that open-source LLMs can be made competitive with targeted domain adaptation._x000a__x0009_4._x0009_Highlights the importance of domain-specific benchmarks in driving progress._x000a__x0009_5._x0009_Future work includes expanding to hybrid paradigms (e.g., MPI+OpenMP, CUDA) and improving reasoning over problem constraints."/>
   </r>
   <r>
     <s v="HPC-GPT: Integrating Large Language Model for High-Performance Computing"/>
@@ -2706,7 +2784,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <s v="Objective:_x000a_To propose HPC-GPT, a novel system that integrates Large Language Models (LLMs) into High-Performance Computing workflows, assisting users with code understanding, generation, and debugging. The system emphasizes practical HPC deployment and domain adaptation via a Retrieval-Augmented Generation (RAG) pipeline._x000a__x000a_Methodology:_x000a__x0009_•_x0009_Introduces an RAG-based architecture that enriches LLMs with HPC-specific knowledge._x000a_Core components:_x000a__x0009_•_x0009_Semantic Indexing over HPC documentation and codebases_x000a__x0009_•_x0009_Retriever module (BM25, dense retrieval)_x000a__x0009_•_x0009_GPT-3.5 / GPT-4 backend for question answering, code generation_x000a_Evaluated via:_x000a__x0009_•_x0009_Real-world HPC code tasks (e.g., OpenMP, MPI)_x000a__x0009_•_x0009_Expert human evaluation (correctness, relevance)_x000a__x0009_•_x0009_Case studies with users from TACC and NSCC_x000a_Introduced HPC-QA, a 1,500-sample QA dataset from HPC tutorials and documentation._x000a__x000a__x0009_•_x0009_HPC-GPT significantly improves LLM output quality across HPC-specific queries._x000a__x0009_•_x0009_QA accuracy improves by ~13%, and subjective scores (relevance, usefulness) by over 1 point (out of 5)._x000a__x0009_•_x0009_In OpenMP/MPI code generation tasks, correctness improved when the RAG component retrieved task-relevant materials._x000a__x000a_User Study Results_x000a__x0009_•_x0009_Conducted with 8 HPC experts and 10 engineers._x000a__x0009_•_x0009_Over 85% preferred HPC-GPT over vanilla ChatGPT for HPC code assistance._x000a__x0009_•_x0009_Noted improvements in:_x000a__x0009_•_x0009_Understanding legacy code_x000a__x0009_•_x0009_Fixing compiler/runtime errors_x000a__x0009_•_x0009_Writing optimized parallel constructs_x000a__x000a_Conclusions_x000a__x0009_1._x0009_HPC-GPT improves LLM accuracy and relevance for HPC tasks by combining retrieval-augmented generation with semantic search over curated HPC corpora._x000a__x0009_2._x0009_Demonstrates the value of contextual grounding — even GPT-4 improves significantly when aided with relevant domain materials._x000a__x0009_3._x0009_Outperforms standalone GPT-3.5/4 in both correctness and user satisfaction for parallel code debugging and generation._x000a__x0009_4._x0009_Highlights the feasibility of RAG architectures in HPC without needing to fine-tune models._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Automated document ingestion_x000a__x0009_•_x0009_Support for hybrid programming paradigms_x000a__x0009_•_x0009_Extending to performance debugging and optimization suggestions"/>
   </r>
   <r>
     <s v="Improving Parallel Program Performance with LLM Optimizers via Agent-System Interface"/>
@@ -2716,7 +2793,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <s v="Objective:_x000a_To design and evaluate an LLM-driven agent framework that optimizes parallel program performance through system-level interaction. The approach emphasizes dynamic feedback and iterative refinement by the LLM to improve execution time, not just correctness._x000a__x000a_Methodology:_x000a_Proposed a closed-loop framework where an LLM agent interacts with the:_x000a__x0009_•_x0009_Compiler_x000a__x0009_•_x0009_Runtime system_x000a__x0009_•_x0009_Profiler_x000a__x0009_•_x0009_Execution environment_x000a_Agent capabilities:_x000a__x0009_•_x0009_Analyze program hotspots_x000a__x0009_•_x0009_Propose code edits or pragma changes (e.g., OpenMP scheduling)_x000a__x0009_•_x0009_Re-run code, assess speedup, and iteratively refine_x000a_Evaluated on:_x000a__x0009_•_x0009_Polybench/C 4.2 benchmark (15 parallel kernels)_x000a__x0009_•_x0009_Optimized using OpenMP pragmas_x000a__x0009_•_x0009_Compared against: baseline code, compiler flags (-O3), GPT-4 without agent interface_x000a__x000a__x0009_•_x0009_The agent-based iterative refinement delivers the highest average speedup._x000a__x0009_•_x0009_GPT-4 alone improves performance, but lacks the dynamic guidance the agent system provides._x000a__x0009_•_x0009_Compiler-only optimizations perform worst across most kernels._x000a__x000a_Correctness_x000a__x0009_•_x0009_All modified codes passed functional verification tests._x000a__x0009_•_x0009_The agent avoids producing invalid parallel patterns thanks to runtime feedback._x000a__x000a_Agent Framework Characteristics_x000a_Includes:_x000a__x0009_•_x0009_Profiler loop to identify hotspots_x000a__x0009_•_x0009_LLM editor to suggest pragma/code changes_x000a__x0009_•_x0009_Validation runner to test correctness and re-profile_x000a_Example modifications:_x000a__x0009_•_x0009_Loop tiling/blocking_x000a__x0009_•_x0009_Schedule clause tuning (static, dynamic, guided)_x000a__x0009_•_x0009_Reduction variable reordering_x000a_Optimizations tailored per program, not one-size-fits-all._x000a__x000a_Conclusions_x000a__x0009_1._x0009_LLM agents can optimize parallel programs beyond static compiler optimizations._x000a__x0009_2._x0009_Iterative interaction with the system environment allows context-aware refinements that general LLM prompting misses._x000a__x0009_3._x0009_Achieves up to 4.3× speedup, with consistent gains across 15 kernels._x000a__x0009_4._x0009_Demonstrates the feasibility of non-fine-tuned LLMs (e.g., GPT-4) as HPC code optimizers, when guided by structured feedback._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Expanding to MPI, CUDA_x000a__x0009_•_x0009_Leveraging fine-tuned LLMs for improved generalization_x000a__x0009_•_x0009_Automating performance-aware code generation in more domains"/>
   </r>
   <r>
     <s v="Large Language Model Evaluation for High-Performance Computing Software Development"/>
@@ -2726,7 +2802,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization, Evaluation &amp; Benchmarking, Code Generation"/>
-    <s v="Objective:_x000a_To evaluate the effectiveness of Large Language Models (LLMs), especially GPT-3.5, in supporting real-world HPC software development tasks, using realistic prompts drawn from production HPC codes at LLNL. The study aims to bridge the gap between academic benchmarks and production-relevant evaluations._x000a__x000a_Methodology:_x000a_Developed a prompt benchmark consisting of 32 prompts across three real-world HPC codes:_x000a__x0009_•_x0009_RAJA, Umpire, CHAI_x000a_Prompt categories include:_x000a__x0009_•_x0009_Code comprehension_x000a__x0009_•_x0009_Bug localization_x000a__x0009_•_x0009_Feature implementation_x000a_Evaluated GPT-3.5 (via OpenAI API) responses based on:_x000a__x0009_•_x0009_Human expert scoring_x000a__x0009_•_x0009_Graded on: Correctness, Completeness, Helpfulness_x000a_Ground truth defined collaboratively with HPC domain experts_x000a__x000a__x0009_•_x0009_Comprehension tasks performed best — GPT-3.5 provides helpful and mostly correct explanations._x000a__x0009_•_x0009_Struggles in code modification, especially implementing new features in complex, modular HPC frameworks._x000a__x0009_•_x0009_Bug localization moderately successful but less reliable in identifying root causes in larger codebases._x000a__x000a_Comparison With Human Developers_x000a__x0009_•_x0009_In side-by-side testing:_x000a__x0009_•_x0009_GPT-3.5 saved time on documentation lookup and quick exploration._x000a__x0009_•_x0009_However, human validation was always needed for code edits._x000a__x0009_•_x0009_Experts noted LLM output as a useful co-pilot, not a replacement._x000a__x000a__x0009_•_x0009_LLMs show high semantic capability, but limited procedural generation skills when deep domain knowledge is required._x000a__x000a_Conclusions_x000a__x0009_1._x0009_GPT-3.5 performs well in comprehension and documentation-related HPC tasks, but poorly in writing or modifying complex code._x000a__x0009_2._x0009_LLMs are useful assistants, not autonomous developers, especially for safety- and performance-critical HPC software._x000a__x0009_3._x0009_Prompt engineering matters — reframing a request for explanation yields better results than asking for a direct implementation._x000a__x0009_4._x0009_Authors advocate for HPC-specific LLM benchmarks based on production codebases, moving beyond synthetic datasets._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Larger sample sizes_x000a__x0009_•_x0009_Comparative testing with GPT-4 and open models_x000a__x0009_•_x0009_Integration with IDEs for live co-pilot testing in HPC teams"/>
   </r>
   <r>
     <s v="LLM as HPC Expert: Extending RAG Architecture for HPC Data"/>
@@ -2736,7 +2811,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Frameworks &amp; Architectures"/>
-    <s v="Objective:_x000a_To explore how Large Language Models (LLMs) can be transformed into expert assistants for High-Performance Computing (HPC) by extending Retrieval-Augmented Generation (RAG) with specialized tooling and multi-source HPC data integration._x000a__x000a_Methodology:_x000a_Built LLM-HPC, a domain-specific assistant incorporating:_x000a__x0009_•_x0009_An extended RAG pipeline with:_x000a__x0009_•_x0009_Custom index building_x000a__x0009_•_x0009_Data curation from HPC logs, docs, user guides_x000a__x0009_•_x0009_Specialized prompt chaining and multi-modal inputs_x000a__x0009_•_x0009_Ability to handle code, logs, and configuration files_x000a_System capabilities:_x000a__x0009_•_x0009_Answer domain-specific questions_x000a__x0009_•_x0009_Debug job failures (e.g., SLURM, MPI)_x000a__x0009_•_x0009_Analyze performance metrics_x000a_Evaluated via:_x000a__x0009_•_x0009_Benchmarked QA tasks_x000a__x0009_•_x0009_Real-world debugging sessions_x000a__x0009_•_x0009_Comparisons to standard GPT-4 answers_x000a__x000a__x0009_•_x0009_LLM-HPC significantly outperforms GPT-4 alone, especially on complex debugging queries and multi-file analysis._x000a__x0009_•_x0009_Gains are attributed to retrieving domain-specific knowledge (job logs, node specs, MPI errors) that GPT-4 otherwise lacks._x000a__x000a_Use Case Successes_x000a__x0009_•_x0009_Job failure analysis: e.g., incorrect SLURM node allocation, MPI segmentation faults_x000a__x0009_•_x0009_Performance tuning: LLM-HPC successfully recommended optimization flags and load balancing strategies based on retrieved docs_x000a__x0009_•_x0009_Error resolution: provided complete sequences of commands to fix environment misconfigurations (e.g., mismatched CUDA versions)_x000a__x000a_Architecture Features_x000a_Modular pipeline:_x000a__x0009_•_x0009_Pre-processing modules for logs and configs_x000a__x0009_•_x0009_Dynamic retriever switching between textual and structured data_x000a__x0009_•_x0009_Context-aware reranking of retrieved documents_x000a_Interfaces:_x000a__x0009_•_x0009_Supports CLI, VS Code extension, and Jupyter integration_x000a_Model backend: GPT-4, but designed to support plug-and-play LLMs_x000a__x000a__x0009_•_x0009_All architectural components substantially contribute to LLM-HPC’s effectiveness._x000a__x0009_•_x0009_Most impactful: retrieval layer and prompt chaining_x000a__x000a_Conclusions_x000a__x0009_1._x0009_LLMs can act as HPC experts when paired with a well-designed RAG system tailored to HPC environments._x000a__x0009_2._x0009_Retrieval, reranking, and chaining mechanisms are critical to success — GPT-4 alone underperforms significantly._x000a__x0009_3._x0009_LLM-HPC demonstrates real-world utility in debugging, resource tuning, and system configuration._x000a__x0009_4._x0009_Encourages the adoption of LLM agents with domain-specific augmentation, rather than relying on zero-shot models._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Expanding to training job optimization, multi-user scheduling_x000a__x0009_•_x0009_Applying models like Claude, Gemini, open-source fine-tuned variants_x000a__x0009_•_x0009_Automating ingestion pipelines for HPC centers"/>
   </r>
   <r>
     <s v="chatHPC: Empowering HPC users with large language models"/>
@@ -2746,7 +2820,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization, Evaluation &amp; Benchmarking, Frameworks &amp; Architectures"/>
-    <s v="Objective:_x000a_To design and evaluate chatHPC, an LLM-based assistant optimized for interacting with HPC users, helping them navigate HPC systems, write batch scripts, debug errors, and understand software stack configurations using a combination of natural language interaction and structured HPC knowledge._x000a__x000a_Methodology:_x000a_Developed chatHPC, an instruction-tuned LLM based on BLOOMZ-7B1-mt, fine-tuned on:_x000a__x0009_•_x0009_~30K HPC-specific instruction-response pairs_x000a__x0009_•_x0009_Sources include real job scripts, logs, error reports, system documentation_x000a_System architecture includes:_x000a__x0009_•_x0009_Chat-based UI_x000a__x0009_•_x0009_HPC knowledge base (retrieval-augmented)_x000a__x0009_•_x0009_Log parsing and suggestion module_x000a_Evaluated against:_x000a__x0009_•_x0009_GPT-3.5-Turbo (zero-shot)_x000a__x0009_•_x0009_GPT-4 (zero-shot)_x000a__x0009_•_x0009_Human experts (for ground-truth validation)_x000a_Benchmarked on 600 HPC user prompts categorized into:_x000a__x0009_•_x0009_Job submission_x000a__x0009_•_x0009_Environment configuration_x000a__x0009_•_x0009_Module loading_x000a__x0009_•_x0009_Error troubleshooting_x000a__x000a__x0009_•_x0009_chatHPC outperforms GPT-4 by &gt;20% on average across real HPC interaction tasks._x000a__x0009_•_x0009_GPT-3.5 consistently underperforms in accuracy and usefulness._x000a__x000a_User Study_x000a_12 HPC users rated system responses on a 1–5 scale:_x000a__x0009_•_x0009_Helpfulness: 4.7 (chatHPC) vs. 3.5 (GPT-4)_x000a__x0009_•_x0009_Correctness: 4.6 (chatHPC) vs. 3.2 (GPT-4)_x000a_Users appreciated clarity of steps, correct flags, and contextual accuracy in chatHPC responses._x000a__x000a_Conclusions_x000a__x0009_1._x0009_chatHPC significantly outperforms GPT-4 and GPT-3.5 in practical HPC user interactions._x000a__x0009_2._x0009_Instruction-tuned open-source models can deliver high accuracy when trained on domain-specific HPC datasets._x000a__x0009_3._x0009_Demonstrates that LLMs can be adapted to supercomputing environments without requiring massive proprietary backends._x000a__x0009_4._x0009_Advocates for domain-specific tuning over general-purpose prompting for operational utility._x000a__x0009_5._x0009_Future directions:_x000a__x0009_•_x0009_Extending to hybrid paradigms (MPI+OpenMP)_x000a__x0009_•_x0009_Integrating real-time job monitoring and error detection_x000a__x0009_•_x0009_Exploring multi-modal inputs (e.g., visual logs or performance traces)"/>
   </r>
   <r>
     <s v="BRIDGING AI AND HPC: A COMPREHENSIVE ANALYSIS OF LARGE LANGUAGE MODEL INTEGRATION IN HIGH-PERFORMANCE COMPUTING ENVIRONMENTS"/>
@@ -2756,7 +2829,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Challenges &amp; Landscape"/>
-    <s v="This paper investigates the systematic integration of Large Language Models (LLMs) into High-Performance Computing (HPC) systems across a wide range of scientific and engineering domains. Through mixed-methods research (case studies, performance benchmarks, and user surveys), it presents evidence that LLMs can significantly enhance workflow efficiency, code optimization, and data interpretation._x000a__x000a_The study spans domains such as climate science, genomics, aerospace, healthcare, and engineering, using empirical results to argue for the transformative synergy between LLMs and HPC._x000a__x000a_Key Contributions:_x000a__x0009_•_x0009_Demonstrates real-world case studies of LLM-HPC integration across diverse fields._x000a__x0009_•_x0009_Shows measurable performance gains, including:_x000a__x0009_•_x0009_25% faster code execution_x000a__x0009_•_x0009_30% better resource utilization_x000a__x0009_•_x0009_40% reduction in time spent on routine tasks_x000a__x0009_•_x0009_Reveals 85% user satisfaction with improved HPC accessibility._x000a__x0009_•_x0009_Presents LLM applications in:_x000a__x0009_•_x0009_Code generation and optimization_x000a__x0009_•_x0009_Workflow management_x000a__x0009_•_x0009_Scientific data analysis_x000a__x000a_Methodology Highlights:_x000a__x0009_•_x0009_Case study-based evaluation across diverse scientific fields._x000a__x0009_•_x0009_Quantitative performance benchmarking and qualitative user feedback via interviews and surveys._x000a__x0009_•_x0009_Use of domain-specific LLMs trained on expert corpora (e.g., climate science literature, structural performance data)._x000a__x0009_•_x0009_Integration of LLMs into live HPC workflows for code assistance, workflow orchestration, and data analysis._x000a__x000a_Future Directions:_x000a__x0009_•_x0009_Hardware-aware LLMs tailored to specific HPC architectures._x000a__x0009_•_x0009_LLM agents for exascale computing, real-time energy grid optimization, and quantum computing._x000a__x0009_•_x0009_Interdisciplinary collaborations (e.g., LLMs + biomedical research, climate models, materials science)._x000a__x0009_•_x0009_Explainable LLMs to enhance trust in scientific reasoning._x000a__x000a_Conclusions:_x000a__x0009_•_x0009_LLMs can democratize HPC usage, making systems accessible to non-experts._x000a__x0009_•_x0009_Tangible improvements in efficiency, usability, and research throughput were observed._x000a__x0009_•_x0009_Despite initial integration costs and technical hurdles, LLM-HPC synergy represents a foundational shift in computational science._x000a__x0009_•_x0009_The research charts a clear roadmap for sustainable and scalable LLM adoption in HPC environments."/>
   </r>
   <r>
     <s v="HPC-Coder-V2: Studying Code LLMs Across Low-Resource Parallel Languages"/>
@@ -2766,7 +2838,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Code Generation"/>
-    <s v="Objective_x000a_To analyze the performance of code LLMs on low-resource parallel programming languages (OpenMP, MPI, CUDA, OpenACC, Chapel, OpenCL, SYCL), and to improve generation accuracy through domain-specific fine-tuning. The paper introduces HPC-Coder-V2, a new benchmark and suite of fine-tuned LLMs._x000a__x000a_Methodology:_x000a__x0009_•_x0009_Introduced a new benchmark with:_x000a__x0009_•_x0009_6,162 examples across 7 parallel programming models_x000a__x0009_•_x0009_Tasks: code generation from docstrings (function-level prompts)_x000a_Evaluated 11 code LLMs including:_x000a__x0009_•_x0009_GPT-3.5, GPT-4_x000a__x0009_•_x0009_StarCoder, CodeLlama (various sizes)_x000a__x0009_•_x0009_WizardCoder, DeepSeek-Coder_x000a__x0009_•_x0009_HPC-Coder-V2 (fine-tuned on 4,914 samples from the benchmark)_x000a_Metric: Functional correctness using unit tests (pass@1)_x000a__x000a__x0009_•_x0009_HPC-Coder-V2 outperforms all other models across every language._x000a__x0009_•_x0009_Gains over GPT-4 range from 10% to 17%, with the highest improvement seen in SYCL and OpenCL (low-resource domains)._x000a__x0009_•_x0009_GPT-4 is the best closed-source baseline but still lags significantly behind HPC-Coder-V2._x000a__x000a__x0009_•_x0009_High-resource: OpenMP, CUDA_x000a__x0009_•_x0009_Low-resource: Chapel, OpenACC, OpenCL, SYCL_x000a__x0009_•_x0009_LLMs struggle most with low-resource languages, unless fine-tuned (e.g., GPT-4 &lt; 52% in OpenACC, SYCL)._x000a__x000a_Model Fine-Tuning and Scaling_x000a__x0009_•_x0009_HPC-Coder-V2 is based on Mistral-7B with LoRA fine-tuning._x000a__x0009_•_x0009_Used only ~4,900 examples for fine-tuning → high efficiency in training._x000a__x0009_•_x0009_The model generalizes better to new problems and unseen domains._x000a__x000a__x0009_•_x0009_Few-shot prompting (2-shot) improves GPT models marginally (+3–4%) but does not close the gap with HPC-Coder-V2._x000a__x0009_•_x0009_Reinforces the benefit of domain-specialized fine-tuning over prompt engineering alone._x000a__x000a_Conclusions_x000a__x0009_1._x0009_HPC-Coder-V2 significantly raises the bar for parallel code generation, especially in low-resource domains._x000a__x0009_2._x0009_Shows that LLMs like Mistral-7B can outperform GPT-4 in niche coding tasks when properly fine-tuned._x000a__x0009_3._x0009_Highlights major performance gaps of general-purpose LLMs on HPC languages like SYCL, OpenACC, and Chapel._x000a__x0009_4._x0009_Demonstrates that modest training data (~5K examples) can yield state-of-the-art results with LoRA._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Scaling to hybrid models (e.g., MPI+OpenMP)_x000a__x0009_•_x0009_Extending support to performance evaluation_x000a__x0009_•_x0009_Incorporating execution constraints and runtime profiling into training"/>
   </r>
   <r>
     <s v="Scope is all you need: Transforming LLMs for HPC Code"/>
@@ -2776,7 +2847,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <s v="Objective:_x000a_The paper challenges the necessity of massive, general-purpose LLMs for HPC tasks. Instead, it introduces domain-specific models designed for High Performance Computing (HPC) code, specifically proposing:_x000a__x0009_•_x0009_TOKOMPILER: A custom tokenizer optimized for HPC code._x000a__x0009_•_x0009_COMPCODER: A modified PolyCoder model using TOKOMPILER for better performance and efficiency in understanding and generating Fortran, C, and C++ code._x000a__x000a_Methodology_x000a_Tokenizer Innovation:_x000a__x0009_•_x0009_TOKOMPILER removes natural language and anonymizes identifiers to strip human semantics._x000a__x0009_•_x0009_Leverages Abstract Syntax Tree (AST) structure to generate consistent, compact, and semantics-free token streams._x000a__x0009_•_x0009_Dramatically reduces token vocabulary (~1,177 tokens) compared to traditional Byte Pair Encoding (BPE) (&gt;50K tokens)._x000a_Modeling:_x000a__x0009_•_x0009_Used PolyCoder (baseline) vs. COMPCODER (PolyCoder + TOKOMPILER)._x000a__x0009_•_x0009_Trained on HPCorpus: ~300K repos (Fortran, C, C++), ~70GB, ~9M files, ~155M functions._x000a__x0009_•_x0009_Evaluated both small (162M) and large (2.8B) models with controlled architecture and training regimes._x000a__x000a__x0009_•_x0009_COMPCODER generalizes better due to cleaner, structure-based tokenization and no human-named identifiers._x000a__x0009_•_x0009_Fine-tuning a multilingual PolyCoder model yielded worse results (perplexity = 2.20), highlighting the value of training from scratch on domain-specific data._x000a__x0009_•_x0009_TOKOMPILER introduces only 0.08% OOV tokens, showing efficient vocabulary design._x000a__x000a_Contributions_x000a__x0009_•_x0009_Redefines tokenization for code modeling by explicitly removing semantics that mislead LLMs and focusing on structural comprehension._x000a__x0009_•_x0009_Demonstrates that smaller, domain-tuned models can outperform larger, generalist ones—both in speed and accuracy._x000a__x0009_•_x0009_First to show that semantics-agnostic LLMs can still comprehend design patterns and code behavior._x000a__x000a_Conclusions_x000a__x0009_1._x0009_Domain-specific LLMs are superior to large general-purpose models for HPC programming tasks—more accurate, faster, and cheaper to train._x000a__x0009_2._x0009_Tokenization is critical: Replacing BPE with TOKOMPILER improves perplexity by up to 35% and reduces training time by 75% for large models._x000a__x0009_3._x0009_Demonstrates that removing natural language and human-chosen variable names does not impair—and may even enhance—code understanding._x000a__x0009_4._x0009_COMPCODER models are more memory-efficient and offer better generalization._x000a__x000a_Future Work_x000a__x0009_•_x0009_Apply TOKOMPILER to more datasets (C/C++) and integrate with Data Flow Graphs (DFG) and Intermediate Representations (IR)._x000a__x0009_•_x0009_Fine-tune COMPCODER for OpenMP pragma generation, MPI domain decomposition, and other HPC code transformation tasks._x000a__x0009_•_x0009_Explore systematic redesign of all LLM components (data, model, tokenizer, objectives) for HPC-specific applications."/>
   </r>
   <r>
     <s v="Comparing Llama-2 and GPT-3 LLMs for HPC kernels generation"/>
@@ -2786,7 +2856,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Code Generation"/>
-    <s v="Objective:_x000a__x000a_To compare the HPC kernel generation capabilities of GPT-3 (code-davinci-002) and LLaMA-2-13B-chat, evaluating their code quality, correctness, and performance for basic parallel computing problems (e.g., stencil, reduce, dot product) in C++ using OpenMP._x000a__x000a_Methodology:_x000a_Focused on 8 core HPC algorithmic patterns:_x000a__x0009_•_x0009_Stencil, Dot Product, Reduce, SAXPY, Transpose, Matrix Mult, Convolution, and Argmax._x000a_Tasks:_x000a__x0009_•_x0009_Prompted each LLM to generate C++ implementations with OpenMP pragmas._x000a__x0009_•_x0009_Executed and evaluated generated code on:_x000a__x0009_•_x0009_Correctness_x000a__x0009_•_x0009_Performance (execution time)_x000a__x0009_•_x0009_Parallelism (OpenMP usage)_x000a_Models:_x000a__x0009_•_x0009_GPT-3 (code-davinci-002)_x000a__x0009_•_x0009_LLaMA-2-13B-chat (HuggingFace/Transformers)_x000a_Each model was tested with 3–5 prompts per task (total ~24 generations)._x000a__x000a__x0009_•_x0009_GPT-3 consistently produces correct code, while LLaMA-2 exhibits semantic and syntactic issues, especially in more complex operations like convolution and reduction._x000a__x0009_•_x0009_LLaMA-2 struggles with OpenMP pragma placement and loop nesting logic._x000a__x000a_Performance (Execution Time on Test Benchmarks)_x000a__x0009_•_x0009_When both models generated correct code:_x000a__x0009_•_x0009_GPT-3’s code generally had slightly better performance, but differences were small (within 5–10%)._x000a__x0009_•_x0009_Performance was more dependent on correctness than model type._x000a__x000a_OpenMP Parallelism Usage_x000a_GPT-3:_x000a__x0009_•_x0009_Correctly uses #pragma omp parallel for in all cases._x000a_LLaMA-2:_x000a__x0009_•_x0009_Often omits or misplaces pragmas, even when otherwise generating valid loops._x000a__x000a_Observations and Limitations_x000a__x0009_•_x0009_LLaMA-2 required prompt tuning and retries to achieve working results; not as reliable in zero-shot settings._x000a__x0009_•_x0009_GPT-3 (code-davinci-002) is more robust, likely due to proprietary training and larger dataset curation._x000a__x0009_•_x0009_Neither model used performance-enhancing details like cache blocking or vectorization._x000a__x000a_Conclusions_x000a__x0009_1._x0009_GPT-3 significantly outperforms LLaMA-2 in correctness for HPC kernel generation (100% vs. 72.5%)._x000a__x0009_2._x0009_LLaMA-2 can generate functional code, but requires prompt iteration and validation, and is prone to structural errors._x000a__x0009_3._x0009_Performance of working code is similar, but GPT-3 is more consistent and reliable in generating parallel OpenMP constructs._x000a__x0009_4._x0009_Study emphasizes that code correctness and syntactic structure are key bottlenecks in open LLMs like LLaMA-2._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Expanding model comparison to GPT-4, CodeLlama, etc._x000a__x0009_•_x0009_Testing larger code bases_x000a__x0009_•_x0009_Incorporating runtime feedback or fine-tuning for improved reliability"/>
   </r>
   <r>
     <s v="AutoParLLM: GNN-guided Context Generation for Zero-Shot Code Parallelization using LLMs"/>
@@ -2796,7 +2865,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <s v="Objective:_x000a_To enable zero-shot parallelization of serial code using LLMs by automatically generating the right context with the help of Graph Neural Networks (GNNs). The authors propose AutoParLLM, a framework that bridges the semantic gap between serial code and parallel constructs by:_x000a__x0009_•_x0009_Using GNNs to extract dataflow and dependency context_x000a__x0009_•_x0009_Guiding LLMs (e.g., GPT-3.5) to insert correct OpenMP pragmas in critical loops_x000a__x000a_Methodology:_x000a_AutoParLLM pipeline:_x000a__x0009_1._x0009_Parse serial code into an Abstract Syntax Tree (AST) and Control Flow Graph (CFG)_x000a__x0009_2._x0009_Use GNN (GraphCodeBERT fine-tuned) to identify parallelizable loops_x000a__x0009_3._x0009_Create context prompts that help LLMs insert appropriate OpenMP pragmas_x000a__x0009_4._x0009_Evaluate correctness and performance of generated code_x000a_Evaluated on:_x000a__x0009_•_x0009_PolyBench/C (32 real-world numerical kernels)_x000a__x0009_•_x0009_Compared against:_x000a__x0009_•_x0009_GPT-3.5 with naive prompting (no context)_x000a__x0009_•_x0009_GPT-3.5 with manual expert context_x000a__x0009_•_x0009_LLVM’s Polly optimizer_x000a_Metrics:_x000a__x0009_•_x0009_Correctness (functional output match)_x000a__x0009_•_x0009_Speedup (vs. serial baseline)_x000a__x0009_•_x0009_Overlap with ground truth OpenMP pragmas_x000a__x000a__x0009_•_x0009_AutoParLLM achieves the highest correctness and speedup, surpassing Polly and GPT-3.5 with manual prompting._x000a__x0009_•_x0009_Naive LLM use underperforms due to lack of structural context._x000a__x0009_•_x0009_GNN-guided context improves LLM’s code generation by aligning prompts with dependency-aware loop candidates._x000a__x000a_Breakdown Observations_x000a__x0009_•_x0009_Parallelization Type Accuracy:_x000a__x0009_•_x0009_AutoParLLM often chose correct schedule types (e.g., static, dynamic)_x000a__x0009_•_x0009_Failure Modes in naive GPT-3.5:_x000a__x0009_•_x0009_Incorrect pragma placement_x000a__x0009_•_x0009_Parallelizing non-safe loops (e.g., with data dependencies)_x000a__x0009_•_x0009_GNN module trained on loop-level labels derived from existing OpenMP annotations in PolyBench_x000a__x000a_Conclusions_x000a__x0009_1._x0009_Zero-shot LLM-based parallelization is viable when paired with GNN-guided context generation._x000a__x0009_2._x0009_AutoParLLM outperforms static compiler optimization (Polly) and GPT-3.5 baseline in both correctness and speedup._x000a__x0009_3._x0009_Framework offers a scalable way to use general-purpose LLMs for domain-specific code transformation without fine-tuning._x000a__x0009_4._x0009_Key to success is the automatic selection and synthesis of context that highlights loop behavior and dependencies._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Extending to MPI or hybrid paradigms_x000a__x0009_•_x0009_Generalizing to other LLMs (e.g., Claude, CodeLlama)_x000a__x0009_•_x0009_Using reinforcement learning for iterative refinement"/>
   </r>
   <r>
     <s v="Do Large Language Models Understand Performance Optimization?"/>
@@ -2806,7 +2874,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <s v="Objective:_x000a_To investigate whether LLMs understand and can apply performance optimization principles in code generation. The paper introduces OptiCode, a benchmark to evaluate LLMs’ ability to generate, recognize, and explain performance-optimized code across key categories such as loop fusion, unrolling, blocking, vectorization, and memory reuse._x000a__x000a_Methodology:_x000a_Developed OptiCode, a benchmark containing:_x000a__x0009_•_x0009_Generation tasks: Prompt LLMs to write optimized code._x000a__x0009_•_x0009_Classification tasks: Identify optimized vs. unoptimized code._x000a__x0009_•_x0009_Explanation tasks: Justify performance differences between code versions._x000a_Optimization categories:_x000a__x0009_•_x0009_Loop fusion, unrolling, blocking, vectorization, memory reuse_x000a_Models tested:_x000a__x0009_•_x0009_GPT-4, GPT-3.5, Claude, Bard, CodeGen-16B, StarCoder_x000a_Evaluation Metrics:_x000a__x0009_•_x0009_Correctness (functional)_x000a__x0009_•_x0009_Performance awareness (execution time and code reasoning)_x000a__x0009_•_x0009_Human expert scoring_x000a__x000a__x0009_•_x0009_GPT-4 consistently outperforms others in all optimization categories._x000a__x0009_•_x0009_Open models (CodeGen, StarCoder) fall significantly behind, especially in blocking and unrolling._x000a__x000a_Classification &amp; Explanation Tasks (GPT-4 only)_x000a__x0009_•_x0009_Classification accuracy: ~83%_x000a_Explanation Quality (Human-rated):_x000a__x0009_•_x0009_GPT-4: 4.3 / 5_x000a__x0009_•_x0009_GPT-3.5: 3.2 / 5_x000a__x0009_•_x0009_Claude: 3.5 / 5_x000a__x000a_Observations_x000a__x0009_•_x0009_LLMs can generate syntactically correct but semantically flawed optimizations (e.g., invalid loop fusion)._x000a__x0009_•_x0009_Explanations often hallucinate compiler behavior or incorrect optimization rationales._x000a__x0009_•_x0009_GPT-4 shows some understanding of tradeoffs (e.g., cache vs. parallelism), but lacks consistency._x000a__x0009_•_x0009_Prompt sensitivity is high — small changes affect whether optimizations are applied._x000a__x000a_Conclusions_x000a__x0009_1._x0009_LLMs have a partial understanding of performance optimization, with GPT-4 leading but still falling short of human-level accuracy and reasoning._x000a__x0009_2._x0009_Generation tasks are more challenging than recognition or explanation, indicating that understanding optimization intent is easier than execution._x000a__x0009_3._x0009_Open-source models struggle significantly with optimization logic, limiting their use in performance-critical contexts._x000a__x0009_4._x0009_The OptiCode benchmark reveals current LLMs are better at recognizing and describing optimizations than producing correct implementations._x000a__x0009_5._x0009_Future work includes:_x000a__x0009_•_x0009_Integrating runtime feedback_x000a__x0009_•_x0009_Exploring fine-tuning for optimization-aware generation_x000a__x0009_•_x0009_Building LLM co-pilots that pair static analysis with learned models"/>
   </r>
   <r>
     <s v="ChatBLAS: The First AI-Generated and Portable BLAS Library"/>
@@ -2816,7 +2883,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Code Generation"/>
-    <s v="This paper presents ChatBLAS, the first AI-generated and portable library for BLAS Level-1 routines, using LLMs like ChatGPT to generate highly optimized C/C++ codes for CPU and GPU (OpenMP, CUDA, HIP) backends. Built in Julia, ChatBLAS allows users to interactively generate, compile, and benchmark BLAS kernels across multiple hardware platforms._x000a__x000a_ChatBLAS is not only a tool but a testbed for prompt engineering and fine-tuning, showcasing how LLMs can be directed to produce functional, correct, and performant HPC kernels. The system uses Julia for orchestrating interactions with LLMs, compiling the resulting code, and comparing outputs against reference implementations for correctness._x000a__x000a_Key Contributions:_x000a__x0009_•_x0009_First functional portable AI-generated BLAS library, supporting OpenMP, CUDA, and HIP backends._x000a__x0009_•_x0009_Use of prompt engineering improved code correctness significantly (e.g., CUDA: from 66% to 84%)._x000a__x0009_•_x0009_Fine-tuning (on ChatGPT 3.5-Turbo) achieved 100% correctness across all supported backends._x000a__x0009_•_x0009_Performance evaluation shows ChatBLAS is competitive with or outperforms vendor libraries (e.g., AOCL, hipBLAS) in some routines._x000a__x0009_•_x0009_Training and inference pipeline is implemented entirely through Julia functions and scripts, enabling reproducibility and modular testing._x000a__x000a_Methodology Highlights:_x000a__x0009_•_x0009_Prompt Engineering: More detailed instructions (e.g., memory management, thread/block setup) improved LLM output quality._x000a__x0009_•_x0009_Fine-Tuning: JSON-based training with example prompts and desired outputs enabled overfitting towards correct generation (beneficial in this context)._x000a__x0009_•_x0009_Performance Testing: Comparison against MKL, AOCL, cuBLAS, and hipBLAS across Intel/AMD CPUs and NVIDIA/AMD GPUs._x000a__x0009_•_x0009_Focused on single-precision vector-vector operations such as saxpy, sscal, sdot, sasum, sswap_x000a__x000a_Evaluation:_x000a__x000a_Correctness Results (selected from Table II):_x000a__x0009_•_x0009_OpenMP: 100% correct with both models._x000a__x0009_•_x0009_CUDA (ChatGPT 4o): 66% → 84% (with prompt engineering)._x000a__x0009_•_x0009_HIP (ChatGPT 3.5): 75% → 86%._x000a__x000a_Performance Results:_x000a__x0009_•_x0009_On Intel CPUs, performance was close to MKL._x000a__x0009_•_x0009_On AMD CPUs, ChatBLAS outperformed AOCL due to the latter’s lack of parallelized Level-1 routines._x000a__x0009_•_x0009_On GPUs:_x000a__x0009_•_x0009_CUDA: Pre-finetuning underperformed due to overuse of atomics._x000a__x0009_•_x0009_Post-finetuning: 4x speedup for sdot and sasum._x000a__x0009_•_x0009_HIP: ChatBLAS often exceeded hipBLAS performance._x000a__x000a_.Strengths:_x000a__x0009_•_x0009_Demonstrates modular, extensible architecture combining Julia and LLMs._x000a__x0009_•_x0009_Validates LLM viability for portable, performant HPC code generation._x000a__x0009_•_x0009_Illustrates effective use of prompt tuning and fine-tuning to boost both correctness and efficiency._x000a__x0009_•_x0009_Open-source implementation allows reproducibility and extensibility._x000a__x000a_Limitations:_x000a__x0009_•_x0009_Currently limited to Level-1 BLAS; Level-2 and Level-3 operations are more complex and remain future work._x000a__x0009_•_x0009_Heavy reliance on prompt engineering and fine-tuning indicates LLMs are not yet fully robust without supervision._x000a__x0009_•_x0009_Fine-tuning only possible on ChatGPT 3.5-Turbo, not 4o (at time of writing)."/>
   </r>
   <r>
     <s v="P4OMP: Retrieval-Augmented Prompting for OpenMP Parallelism in Serial Code"/>
@@ -2826,7 +2892,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization"/>
-    <m/>
   </r>
   <r>
     <s v="ParEval-Repo: A Benchmark Suite for Evaluating LLMs with Repository-level HPC Translation Tasks"/>
@@ -2836,7 +2901,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Evaluation &amp; Benchmarking"/>
-    <m/>
   </r>
   <r>
     <s v="LLM-Assisted Translation of Legacy FORTRAN Codes to C++: A Cross-Platform Study"/>
@@ -2846,7 +2910,6 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Code Generation"/>
-    <m/>
   </r>
   <r>
     <s v="LLM &amp; HPC:Benchmarking DeepSeek's Performance in High-Performance Computing Tasks"/>
@@ -2856,124 +2919,114 @@
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <s v="Evaluation &amp; Benchmarking"/>
-    <m/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Leveraging Large Language Models for Code Translation and Software Development in Scientific Computing"/>
+    <s v="DhruvDubey2025CodeTranslation"/>
+    <s v="Dhruv, Akash and Dubey, Anshu"/>
     <x v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation, Challenges &amp; Landscape"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Fortran2CPP: Automating Fortran-to-C++ Translation using LLMs via Multi-Turn Dialogue and Dual-Agent Integration"/>
+    <s v="Chen2024Fortran2CPP"/>
+    <s v="Le Chen and Bin Lei and Dunzhi Zhou and Pei{-}Hung Lin and Chunhua Liao and Caiwen Ding and Ali Jannesari"/>
     <x v="16"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="ChatHPC: Building the Foundations for a Productive and Trustworthy AI-Assisted HPC Ecosystem"/>
+    <s v="ValeroLara2025ChatHPC"/>
+    <s v="Pedro Valero Lara and Aaron Young and Jeffrey S. Vetter and Zheming Jin and Swaroop Pophale and Mohammad Alaul Haque Monil and Keita Teranishi and William F. Godoy"/>
     <x v="17"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Frameworks &amp; Architectures"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads"/>
+    <s v="ValeroLara2026ChatMPI"/>
+    <s v="Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy"/>
     <x v="18"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Parallelization &amp; Optimization, Code Generation, Frameworks &amp; Architectures"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="{PRAGMA}: A Profiling-Reasoned Multi-Agent Framework for Automatic Kernel Optimization"/>
+    <s v="Lei2025PRAGMA"/>
+    <s v="Kelun Lei and Hailong Yang and Huaitao Zhang and Xin You and Kaige Zhang and Zhongzhi Luan and Yi Liu and Depei Qian"/>
     <x v="19"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Parallelization &amp; Optimization, Frameworks &amp; Architectures"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Leveraging LLMs to Automate Energy-Aware Refactoring of Parallel Scientific Codes"/>
+    <s v="Dearing2025LASSIEE"/>
+    <s v="Matthew T. Dearing and Yiheng Tao and Xingfu Wu and Zhiling Lan and Valerie Taylor"/>
     <x v="20"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Parallelization &amp; Optimization"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="LLM-HPC++: Evaluating LLM-Generated Modern C++ and MPI+OpenMP Codes for Scalable Mandelbrot Set Computation"/>
+    <s v="Diehl2025LLMHPCpp"/>
+    <s v="Patrick Diehl and Noujoud Nader and Deepti Gupta"/>
     <x v="21"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Evaluation &amp; Benchmarking, Code Generation"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Adding New Capability in Existing Scientific Application with LLM Assistance"/>
+    <s v="DubeyDhruv2025NewCapability"/>
+    <s v="Anshu Dubey and Akash Dhruv"/>
     <x v="22"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation, Challenges &amp; Landscape"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
+    <s v="{PEAK}: A Performance Engineering AI-Assistant for GPU Kernels Powered by Natural Language Transformations"/>
+    <s v="Tariq2025PEAK"/>
+    <s v="Muhammad Usman Tariq and Abhinav Jangda and Angelica Moreira and Madan Musuvathi and Tyler Sorensen"/>
     <x v="23"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Parallelization &amp; Optimization, Frameworks &amp; Architectures"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AC5E488-DAC0-1B46-86E0-729BAED744A6}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
-  <location ref="D8:E34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AC5E488-DAC0-1B46-86E0-729BAED744A6}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="D8:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
-      <items count="25">
+      <items count="34">
         <item x="7"/>
         <item x="2"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
+        <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
         <item x="0"/>
-        <item x="18"/>
-        <item x="19"/>
+        <item m="1" x="27"/>
+        <item m="1" x="28"/>
         <item x="1"/>
-        <item x="20"/>
-        <item x="21"/>
+        <item m="1" x="29"/>
+        <item m="1" x="30"/>
         <item x="6"/>
-        <item x="22"/>
-        <item x="23"/>
+        <item m="1" x="31"/>
+        <item m="1" x="32"/>
         <item x="5"/>
         <item x="4"/>
         <item x="10"/>
@@ -2984,14 +3037,22 @@
         <item x="3"/>
         <item x="12"/>
         <item x="11"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="15">
         <item x="0"/>
         <item x="1"/>
@@ -3011,95 +3072,32 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
+      <items count="7">
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="0"/>
         <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="2">
-    <field x="9"/>
+  <rowFields count="1">
     <field x="8"/>
   </rowFields>
-  <rowItems count="26">
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
     </i>
     <i>
       <x v="2"/>
     </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
+    <i>
       <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -3111,7 +3109,7 @@
   <dataFields count="1">
     <dataField name="Count of Title" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="3">
     <chartFormat chart="2" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -3130,6 +3128,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="8" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -3144,8 +3154,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8C10D0-4D69-4647-9A8C-C5DCBFB845B5}" name="Table1" displayName="Table1" ref="A1:H60" totalsRowShown="0" dataDxfId="8">
-  <autoFilter ref="A1:H60" xr:uid="{0C8C10D0-4D69-4647-9A8C-C5DCBFB845B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8C10D0-4D69-4647-9A8C-C5DCBFB845B5}" name="Table1" displayName="Table1" ref="A1:H73" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="A1:H73" xr:uid="{0C8C10D0-4D69-4647-9A8C-C5DCBFB845B5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4D706761-8EE7-AA48-803E-2E3E91C79AB7}" name="Title" dataDxfId="7"/>
     <tableColumn id="7" xr3:uid="{9B75EE74-A530-994A-A2DD-F4490D8B4AEA}" name="Key" dataDxfId="6"/>
@@ -3497,16 +3507,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABD1113-DFD0-DA42-96EC-95276F75ACF7}">
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H73"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="47.33203125" customWidth="1"/>
+    <col min="1" max="2" width="47.375" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="36.33203125" customWidth="1"/>
-    <col min="8" max="8" width="61.33203125" customWidth="1"/>
+    <col min="7" max="7" width="36.375" customWidth="1"/>
+    <col min="8" max="8" width="61.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3532,7 +3542,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -3554,7 +3564,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="54" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3576,7 +3586,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -3602,7 +3612,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3628,7 +3638,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -3654,7 +3664,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -3680,7 +3690,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -3706,7 +3716,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -3728,7 +3738,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -3750,7 +3760,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="54" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -3772,7 +3782,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -3794,7 +3804,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="195" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -3816,7 +3826,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -3838,7 +3848,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -3860,7 +3870,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -3882,7 +3892,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,7 +3914,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -3926,7 +3936,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -3948,7 +3958,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -3974,7 +3984,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -3996,7 +4006,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -4018,7 +4028,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -4040,7 +4050,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -4062,7 +4072,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -4084,7 +4094,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>57</v>
       </c>
@@ -4106,7 +4116,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -4128,7 +4138,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="54" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>61</v>
       </c>
@@ -4150,7 +4160,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
@@ -4172,7 +4182,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -4194,7 +4204,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>68</v>
       </c>
@@ -4216,7 +4226,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>70</v>
       </c>
@@ -4238,7 +4248,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
@@ -4260,7 +4270,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>74</v>
       </c>
@@ -4282,7 +4292,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>76</v>
       </c>
@@ -4308,7 +4318,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>79</v>
       </c>
@@ -4326,7 +4336,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>81</v>
       </c>
@@ -4348,7 +4358,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>84</v>
       </c>
@@ -4370,7 +4380,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>87</v>
       </c>
@@ -4388,7 +4398,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>89</v>
       </c>
@@ -4406,7 +4416,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>91</v>
       </c>
@@ -4428,7 +4438,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>98</v>
       </c>
@@ -4454,7 +4464,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>100</v>
       </c>
@@ -4480,7 +4490,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>102</v>
       </c>
@@ -4506,7 +4516,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>104</v>
       </c>
@@ -4532,7 +4542,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>107</v>
       </c>
@@ -4558,7 +4568,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>109</v>
       </c>
@@ -4584,7 +4594,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>112</v>
       </c>
@@ -4610,7 +4620,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>115</v>
       </c>
@@ -4632,7 +4642,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>118</v>
       </c>
@@ -4654,7 +4664,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -4676,7 +4686,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>125</v>
       </c>
@@ -4698,7 +4708,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>128</v>
       </c>
@@ -4720,7 +4730,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>131</v>
       </c>
@@ -4742,7 +4752,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8" ht="135" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>134</v>
       </c>
@@ -4764,7 +4774,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>150</v>
       </c>
@@ -4790,7 +4800,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>202</v>
       </c>
@@ -4814,7 +4824,7 @@
       </c>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>204</v>
       </c>
@@ -4838,7 +4848,7 @@
       </c>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>207</v>
       </c>
@@ -4862,7 +4872,7 @@
       </c>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>209</v>
       </c>
@@ -4885,6 +4895,318 @@
         <v>206</v>
       </c>
       <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" s="1">
+        <v>45809</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" s="1">
+        <v>45653</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:8" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D63" s="1">
+        <v>45976</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" spans="1:8" ht="54" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46047</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65" s="1">
+        <v>45970</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D66" s="1">
+        <v>45781</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" s="1">
+        <v>46009</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" s="1">
+        <v>45960</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D69" s="1">
+        <v>46013</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="1">
+        <v>45929</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" s="1">
+        <v>45976</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D72" s="1">
+        <v>45861</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="1:8" ht="54" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D73" s="1">
+        <v>45915</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H73" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -4899,7 +5221,7 @@
           <x14:formula1>
             <xm:f>Dropdowns!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E60</xm:sqref>
+          <xm:sqref>E2:E73</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17F031C1-A368-A04F-8F67-840684ACDCF1}">
           <x14:formula1>
@@ -4915,19 +5237,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC35A1C8-49F2-684E-A589-635057EFC2E0}">
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="113.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="73.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="113.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -4950,486 +5272,740 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="13">
         <v>45323</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="13">
         <v>45413</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="13">
         <v>45413</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="13">
         <v>45200</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="13">
         <v>45778</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="E6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="13">
         <v>45413</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="E7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="13">
         <v>45627</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="E8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="13">
         <v>45597</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="E9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="13">
         <v>45505</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="E10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="13">
         <v>45627</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="E11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="13">
         <v>45170</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="E12" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="13">
         <v>45170</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="E13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="13">
         <v>45689</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="E14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="13">
         <v>45717</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="E15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="13">
         <v>45665</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="E16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="13">
         <v>45836</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="E17" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="13">
         <v>45834</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="E18" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="13">
         <v>45768</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="E19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>45731</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="E20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D21" s="7">
-        <v>45231</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D22" s="7">
-        <v>45261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D23" s="7">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D24" s="7">
-        <v>45352</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D25" s="7">
-        <v>45383</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D26" s="7">
-        <v>45444</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D27" s="7">
-        <v>45474</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D28" s="7">
-        <v>45536</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D29" s="7">
-        <v>45566</v>
+    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="13">
+        <v>45809</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" s="13">
+        <v>45653</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D23" s="13">
+        <v>45976</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" s="13">
+        <v>46047</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D25" s="13">
+        <v>45970</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" s="13">
+        <v>45781</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="13">
+        <v>46009</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" s="13">
+        <v>45960</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D29" s="13">
+        <v>46013</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D30" s="13">
+        <v>45929</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D31" s="13">
+        <v>45976</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D32" s="13">
+        <v>45861</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="13">
+        <v>45915</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5452,33 +6028,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4EE84F-C795-3E47-86D0-27A4DA3A3887}">
-  <dimension ref="D8:E34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="D8:E13"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="131.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="66.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="60.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="131.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="54.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="66.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="60.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="67" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="76.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="78.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="76.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="78.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="52.625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="72" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="67.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="67.625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="83.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="47" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="50" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
         <v>94</v>
       </c>
@@ -5486,7 +6062,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="5" t="s">
         <v>222</v>
       </c>
@@ -5494,177 +6070,36 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D10" s="16" t="s">
-        <v>225</v>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="E10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D11" s="16" t="s">
-        <v>226</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D11" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="E11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D12" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D13" s="16" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D14" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="16" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D16" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D17" s="16" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D18" s="16" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D19" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D20" s="16" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D21" s="16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D22" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D23" s="16" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D24" s="16" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D25" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D26" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D27" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D28" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D29" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D30" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D31" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D32" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D33" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D34" s="5" t="s">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E34">
-        <v>19</v>
+      <c r="E13">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5677,13 +6112,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC8D95E-9776-284B-9481-70E9BE9D9A41}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.33203125" customWidth="1"/>
+    <col min="1" max="1" width="61.375" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -5691,7 +6126,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -5699,7 +6134,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -5707,7 +6142,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -5715,7 +6150,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5723,7 +6158,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -5731,7 +6166,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>143</v>
       </c>

--- a/data/Research Papers.xlsx
+++ b/data/Research Papers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljaljevi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74241B7C-A71A-4B60-B204-E806CCE1BCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16B4DB7-6B2C-4892-87CC-AAB4602317AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{027DABDA-E301-6248-9EF5-B2B8807799A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{027DABDA-E301-6248-9EF5-B2B8807799A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="268">
   <si>
     <t>Title</t>
   </si>
@@ -1333,9 +1333,6 @@
   </si>
   <si>
     <t>Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren</t>
-  </si>
-  <si>
-    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1492,6 +1489,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1727,28 +1727,6 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0"/>
-                  <c:y val="6.685510405806129E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-EA81-4FD4-8DBD-4FC885948BA9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1805,9 +1783,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Timeline Main Research'!$D$9:$D$13</c:f>
+              <c:f>'Timeline Main Research'!$D$9:$D$12</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2023</c:v>
                 </c:pt>
@@ -1817,18 +1795,15 @@
                 <c:pt idx="2">
                   <c:v>2025</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>2026</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Timeline Main Research'!$E$9:$E$13</c:f>
+              <c:f>'Timeline Main Research'!$E$9:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -1836,10 +1811,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2643,9 +2615,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ljaljevic, Strahinja" refreshedDate="46141.403660532407" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{7E58EB42-7530-3042-8255-3A940C0AEDDC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ljaljevic, Strahinja" refreshedDate="46153.435911111112" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{D2FCC20E-3010-47C7-980A-7F2517E1B2F8}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G29" sheet="Raw Main Research"/>
+    <worksheetSource ref="A1:G33" sheet="Raw Main Research"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="Title" numFmtId="0">
@@ -2658,7 +2630,7 @@
       <sharedItems longText="1"/>
     </cacheField>
     <cacheField name="Year" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2026-01-26T00:00:00" count="33">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2025-12-23T00:00:00" count="27">
         <d v="2024-02-01T00:00:00"/>
         <d v="2024-05-01T00:00:00"/>
         <d v="2023-10-01T00:00:00"/>
@@ -2677,21 +2649,15 @@
         <d v="2025-06-01T00:00:00"/>
         <d v="2024-12-27T00:00:00"/>
         <d v="2025-11-15T00:00:00"/>
-        <d v="2026-01-25T00:00:00"/>
+        <d v="2025-12-01T00:00:00"/>
         <d v="2025-11-09T00:00:00"/>
         <d v="2025-05-04T00:00:00"/>
         <d v="2025-12-18T00:00:00"/>
         <d v="2025-10-30T00:00:00"/>
         <d v="2025-12-22T00:00:00"/>
-        <d v="2023-11-01T00:00:00" u="1"/>
-        <d v="2023-12-01T00:00:00" u="1"/>
-        <d v="2024-01-01T00:00:00" u="1"/>
-        <d v="2024-03-01T00:00:00" u="1"/>
-        <d v="2024-04-01T00:00:00" u="1"/>
-        <d v="2024-06-01T00:00:00" u="1"/>
-        <d v="2024-07-01T00:00:00" u="1"/>
-        <d v="2024-09-01T00:00:00" u="1"/>
-        <d v="2024-10-01T00:00:00" u="1"/>
+        <d v="2025-09-29T00:00:00"/>
+        <d v="2025-07-23T00:00:00"/>
+        <d v="2025-09-15T00:00:00"/>
       </sharedItems>
       <fieldGroup par="8"/>
     </cacheField>
@@ -2706,7 +2672,7 @@
     </cacheField>
     <cacheField name="Months (Year)" numFmtId="0" databaseField="0">
       <fieldGroup base="3">
-        <rangePr groupBy="months" startDate="2023-09-01T00:00:00" endDate="2026-01-26T00:00:00"/>
+        <rangePr groupBy="months" startDate="2023-09-01T00:00:00" endDate="2025-12-23T00:00:00"/>
         <groupItems count="14">
           <s v="&lt;9/1/2023"/>
           <s v="Jan"/>
@@ -2721,20 +2687,19 @@
           <s v="Oct"/>
           <s v="Nov"/>
           <s v="Dec"/>
-          <s v="&gt;1/26/2026"/>
+          <s v="&gt;12/23/2025"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
     <cacheField name="Years (Year)" numFmtId="0" databaseField="0">
       <fieldGroup base="3">
-        <rangePr groupBy="years" startDate="2023-09-01T00:00:00" endDate="2026-01-26T00:00:00"/>
-        <groupItems count="6">
+        <rangePr groupBy="years" startDate="2023-09-01T00:00:00" endDate="2025-12-23T00:00:00"/>
+        <groupItems count="5">
           <s v="&lt;9/1/2023"/>
           <s v="2023"/>
           <s v="2024"/>
           <s v="2025"/>
-          <s v="2026"/>
-          <s v="&gt;1/26/2026"/>
+          <s v="&gt;12/23/2025"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
@@ -2748,7 +2713,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="32">
   <r>
     <s v="The Landscape and Challenges of HPC Research and LLMs"/>
     <s v="chen_landscape_2024"/>
@@ -3001,32 +2966,59 @@
     <s v="Y"/>
     <s v="Parallelization &amp; Optimization, Frameworks &amp; Architectures"/>
   </r>
+  <r>
+    <s v="Chat{PORT}: Fine-Tuned {LLM} for Easy Code {PORT}ing"/>
+    <s v="Pophale2026ChatPORT"/>
+    <s v="Swaroop Pophale and Zheming Jin and Keita Teranishi"/>
+    <x v="24"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation, Frameworks &amp; Architectures"/>
+  </r>
+  <r>
+    <s v="Enhancing Chat{PORT} with {CUDA}-to-{SYCL} Kernel Translation Capability"/>
+    <s v="Jin2025ChatPORTCudaSyCL"/>
+    <s v="Zheming Jin and Swaroop Pophale and Keita Teranishi"/>
+    <x v="17"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation, Frameworks &amp; Architectures"/>
+  </r>
+  <r>
+    <s v="{PCEBench}: A Multi-Dimensional Benchmark for Evaluating Large Language Models in Parallel Code Generation"/>
+    <s v="Chen2025PCEBench"/>
+    <s v="L. Chen and N. Ahmed and M. Capot{\u{a}} and T. Willke and N. Hasabnis and A. Jannesari"/>
+    <x v="25"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Evaluation &amp; Benchmarking"/>
+  </r>
+  <r>
+    <s v="{UniPar}: A Unified LLM-Based Framework for Parallel and Accelerated Code Translation in {HPC}"/>
+    <s v="Bitan2025UniPar"/>
+    <s v="Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren"/>
+    <x v="26"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <s v="Code Generation, Frameworks &amp; Architectures"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AC5E488-DAC0-1B46-86E0-729BAED744A6}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="D8:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7DEE0883-C0F8-4128-94F6-E3020B8D5509}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="D8:E12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
-      <items count="34">
+      <items count="28">
         <item x="7"/>
         <item x="2"/>
-        <item m="1" x="24"/>
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
         <item x="0"/>
-        <item m="1" x="27"/>
-        <item m="1" x="28"/>
         <item x="1"/>
-        <item m="1" x="29"/>
-        <item m="1" x="30"/>
         <item x="6"/>
-        <item m="1" x="31"/>
-        <item m="1" x="32"/>
         <item x="5"/>
         <item x="4"/>
         <item x="10"/>
@@ -3040,12 +3032,15 @@
         <item x="15"/>
         <item x="16"/>
         <item x="17"/>
-        <item x="18"/>
         <item x="19"/>
         <item x="20"/>
         <item x="21"/>
         <item x="22"/>
         <item x="23"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3072,13 +3067,12 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
-      <items count="7">
+      <items count="6">
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="0"/>
         <item x="4"/>
-        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3086,7 +3080,7 @@
   <rowFields count="1">
     <field x="8"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -3095,9 +3089,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -3109,7 +3100,7 @@
   <dataFields count="1">
     <dataField name="Count of Title" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="3">
+  <chartFormats count="2">
     <chartFormat chart="2" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -3124,18 +3115,6 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -5296,7 +5275,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -5319,7 +5298,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -5342,7 +5321,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -5365,7 +5344,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -5388,7 +5367,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -5411,7 +5390,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="15" t="s">
         <v>76</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5434,7 +5413,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="15" t="s">
         <v>98</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -5457,7 +5436,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="15" t="s">
         <v>100</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -5480,7 +5459,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -5503,7 +5482,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="15" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -5526,7 +5505,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="15" t="s">
         <v>107</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -5549,7 +5528,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="15" t="s">
         <v>109</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -5572,7 +5551,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="15" t="s">
         <v>112</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -5595,7 +5574,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="15" t="s">
         <v>150</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -5618,7 +5597,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="15" t="s">
         <v>202</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -5641,7 +5620,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="15" t="s">
         <v>204</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -5664,7 +5643,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="15" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -6028,7 +6007,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4EE84F-C795-3E47-86D0-27A4DA3A3887}">
-  <dimension ref="D8:E13"/>
+  <dimension ref="D8:E12"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
@@ -6083,23 +6062,15 @@
         <v>224</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D12" s="5" t="s">
-        <v>268</v>
+        <v>95</v>
       </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
